--- a/data/trans_dic/IP25-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP25-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -518,15 +519,12 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que ven la televisión todos o casi todos los días</t>
+          <t>Menores que ven la televisión todos o casi todos los días (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -537,23 +535,20 @@
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Niño</t>
         </is>
       </c>
+      <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -575,47 +570,32 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
           <t>2007</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2016</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
         </is>
       </c>
     </row>
@@ -631,14 +611,11 @@
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -663,47 +640,32 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>93,06%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
           <t>86,69%</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -716,69 +678,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>77,31; 91,89</t>
+          <t>76,57; 92,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>86,06; 97,31</t>
+          <t>86,49; 97,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76,18; 91,39</t>
+          <t>75,01; 90,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,98</t>
+          <t>79,18; 94,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>81,15; 94,33</t>
+          <t>85,6; 97,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,97; 96,99</t>
+          <t>80,9; 93,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,97; 93,64</t>
+          <t>81,6; 91,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,86</t>
+          <t>88,23; 96,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>82,0; 91,82</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>87,6; 96,14</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>81,3; 90,87</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0; 0,96</t>
+          <t>81,1; 91,16</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -803,47 +750,32 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>87,18%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
           <t>94,18%</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -856,69 +788,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>80,82; 91,68</t>
+          <t>81,49; 92,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>79,09; 90,29</t>
+          <t>78,5; 89,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>87,08; 95,58</t>
+          <t>88,14; 96,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,34</t>
+          <t>81,82; 92,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>82,62; 92,11</t>
+          <t>84,08; 93,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>83,57; 92,89</t>
+          <t>92,12; 98,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>92,31; 98,24</t>
+          <t>83,85; 91,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,22</t>
+          <t>83,54; 90,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>83,81; 90,79</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>82,96; 90,4</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>91,15; 96,21</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0; 0,64</t>
+          <t>91,01; 96,22</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -943,47 +860,32 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>93,09%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
           <t>84,71%</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -996,62 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>84,95; 95,97</t>
+          <t>84,25; 95,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>84,81; 96,06</t>
+          <t>85,61; 96,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>76,93; 91,68</t>
+          <t>75,78; 91,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,96</t>
+          <t>87,51; 97,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>88,27; 97,32</t>
+          <t>88,55; 98,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>88,38; 98,03</t>
+          <t>76,35; 90,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>76,11; 90,18</t>
+          <t>88,94; 95,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,88</t>
+          <t>89,01; 95,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>88,35; 95,71</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>89,02; 96,16</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>79,58; 89,34</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>0; 0,96</t>
+          <t>79,05; 89,05</t>
         </is>
       </c>
     </row>
@@ -1083,47 +970,32 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>90,5%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
           <t>91,16%</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>88,09; 97,5</t>
+          <t>87,55; 97,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>84,13; 95,47</t>
+          <t>84,16; 95,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80,49; 93,31</t>
+          <t>81,12; 93,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,02</t>
+          <t>84,94; 96,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>85,94; 96,38</t>
+          <t>83,39; 94,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,43; 94,9</t>
+          <t>87,87; 97,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,93; 97,73</t>
+          <t>88,76; 95,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>86,18; 93,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>88,48; 95,61</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>86,0; 93,86</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>86,06; 94,28</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0; 1,18</t>
+          <t>86,84; 94,37</t>
         </is>
       </c>
     </row>
@@ -1223,47 +1080,32 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>95,32%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
           <t>88,85%</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>69,98; 89,22</t>
+          <t>70,05; 89,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>87,37; 98,53</t>
+          <t>87,58; 98,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>82,55; 97,18</t>
+          <t>82,67; 96,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>66,19; 86,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>67,05; 86,31</t>
+          <t>87,92; 98,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>88,06; 98,58</t>
+          <t>74,14; 93,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,23; 93,9</t>
+          <t>72,21; 86,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,66</t>
+          <t>90,61; 98,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>71,31; 86,05</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>90,87; 98,36</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>82,16; 93,46</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0; 1,37</t>
+          <t>81,94; 93,45</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1363,47 +1190,32 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>91,53%</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
           <t>92,56%</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -1416,69 +1228,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>84,88; 97,53</t>
+          <t>84,59; 96,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>82,38; 95,93</t>
+          <t>82,02; 95,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>82,3; 95,82</t>
+          <t>83,63; 96,46</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,39</t>
+          <t>82,64; 94,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>83,84; 95,43</t>
+          <t>83,95; 96,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>84,07; 96,44</t>
+          <t>86,75; 97,65</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>86,79; 97,67</t>
+          <t>87,06; 95,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,04</t>
+          <t>85,95; 95,39</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>86,77; 95,08</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>86,14; 95,06</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>87,15; 95,94</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>0; 1,11</t>
+          <t>87,5; 95,84</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1503,47 +1300,32 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>87,32%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
           <t>90,74%</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>89,87; 96,83</t>
+          <t>89,68; 96,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>79,88; 89,92</t>
+          <t>79,9; 90,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>88,48; 95,31</t>
+          <t>87,9; 95,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,08</t>
+          <t>82,62; 91,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>82,77; 91,59</t>
+          <t>84,78; 93,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,91; 93,19</t>
+          <t>84,59; 92,87</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,38; 92,78</t>
+          <t>87,29; 93,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,07</t>
+          <t>83,51; 90,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>87,54; 93,42</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>83,85; 90,31</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>87,61; 93,24</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0; 0,54</t>
+          <t>87,5; 92,96</t>
         </is>
       </c>
     </row>
@@ -1643,47 +1410,32 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>90,33%</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
           <t>91,56%</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>85,84; 93,72</t>
+          <t>85,88; 93,7</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>84,41; 92,68</t>
+          <t>85,32; 92,79</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>85,49; 92,79</t>
+          <t>85,6; 93,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0; 1,0</t>
+          <t>78,43; 87,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>78,1; 87,59</t>
+          <t>86,81; 94,19</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>87,4; 94,49</t>
+          <t>88,98; 95,79</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>89,47; 95,83</t>
+          <t>83,49; 89,49</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,92</t>
+          <t>87,14; 92,7</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>83,3; 89,48</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>87,47; 92,6</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>88,78; 93,64</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0; 0,48</t>
+          <t>89,27; 93,77</t>
         </is>
       </c>
     </row>
@@ -1783,47 +1520,32 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>90,2%</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
           <t>90,6%</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>88,22; 91,98</t>
+          <t>88,45; 92,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>87,15; 90,9</t>
+          <t>86,93; 90,92</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>88,05; 91,54</t>
+          <t>87,75; 91,55</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>85,37; 89,35</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>85,44; 89,42</t>
+          <t>89,6; 92,97</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>89,46; 92,82</t>
+          <t>89,47; 92,83</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>89,59; 92,99</t>
+          <t>87,52; 90,17</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>88,95; 91,44</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>87,56; 90,14</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>88,85; 91,43</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>89,26; 91,8</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>0; 0,1</t>
+          <t>89,15; 91,76</t>
         </is>
       </c>
     </row>
@@ -1904,20 +1611,1627 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="A1:B2"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A14:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que ven la televisión todos o casi todos los días (tasa de respuesta: 99,89%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>45219</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>53525</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>48521</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>53324</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>60230</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>57096</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98543</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>113754</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>105617</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>40252; 48404</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>49668; 55907</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>43036; 52121</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>47681; 56750</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>55478; 63013</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>52152; 60417</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>92029; 103539</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>107849; 117733</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>98809; 111066</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>88817</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>89006</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>96056</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>95665</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99194</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>105716</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>184482</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>188200</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>201772</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>82760; 93690</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>82198; 94123</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>91618; 99836</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>88988; 100281</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>93463; 104021</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>101590; 108332</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>176346; 191705</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>180344; 195711</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>194974; 206134</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>61973</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>62641</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>57001</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>65928</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>67158</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>58824</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>127901</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>129799</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>115824</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>56949; 64844</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>58369; 65459</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>50644; 60953</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>61545; 68450</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>63093; 69860</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>53369; 63152</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>122675; 132232</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>124111; 133797</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>108090; 121766</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>70034</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>70571</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>67828</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>72678</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>74230</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>76338</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>142712</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>144801</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>144165</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>65541; 72941</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>65440; 73970</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>62427; 71737</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>67197; 76160</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>68574; 77962</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>71339; 79178</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>136664; 147265</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>137879; 150218</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>137326; 149244</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>33981</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>41837</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>39756</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>35024</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>44573</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>40017</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>69005</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>86410</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>79773</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>29319; 37334</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>38449; 43256</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>35912; 41747</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>29681; 38692</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>41106; 46084</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>34364; 43144</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>62606; 74618</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>82141; 89150</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>73570; 83905</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>52088</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>50915</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>49423</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>54060</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>55475</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>54255</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>106148</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>106390</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>103679</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>47419; 54183</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>45921; 53694</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>45390; 52352</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>49363; 56731</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>50577; 58317</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>50091; 56382</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100804; 110357</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>99898; 110874</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>98010; 107349</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>119070</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>117465</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>126774</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>119276</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>129245</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>128608</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>238346</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>246709</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>255382</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>114053; 123132</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>110084; 124430</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>120757; 130644</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>112082; 124682</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>122716; 134619</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>121864; 133794</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>229418; 244771</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>235932; 254573</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>246274; 261642</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>428</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>446</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>471</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>142569</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>146922</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>147374</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>136673</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>154748</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>159360</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>279242</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>301669</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>306734</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>135606; 147954</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>140528; 152832</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>140527; 152692</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>128671; 144054</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>146954; 159438</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>152030; 163655</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>268813; 288109</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>291047; 309594</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>299079; 314143</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>915</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>909</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>948</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>951</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>978</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>971</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>1866</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>1887</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>1919</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>613750</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>632881</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>632732</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>632629</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>684852</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>680214</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>1246379</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>1317733</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>1312946</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>601092; 625225</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>617612; 645912</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>618103; 644853</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>616993; 645702</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>672442; 697686</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>666379; 691435</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>1227233; 1264402</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>1299481; 1335811</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>1292026; 1329840</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP25-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP25-Provincia-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>76,57; 92,08</t>
+          <t>77,09; 92,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>86,49; 97,35</t>
+          <t>85,75; 97,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>75,01; 90,85</t>
+          <t>75,62; 91,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>79,18; 94,24</t>
+          <t>80,76; 94,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>85,6; 97,23</t>
+          <t>85,09; 97,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,9; 93,72</t>
+          <t>80,0; 93,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,6; 91,8</t>
+          <t>81,64; 91,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>88,23; 96,32</t>
+          <t>88,06; 96,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>81,1; 91,16</t>
+          <t>81,23; 91,79</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>81,49; 92,25</t>
+          <t>81,79; 92,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>78,5; 89,89</t>
+          <t>78,62; 89,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88,14; 96,04</t>
+          <t>87,45; 95,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>81,82; 92,21</t>
+          <t>82,45; 92,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>84,08; 93,58</t>
+          <t>82,75; 93,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>92,12; 98,23</t>
+          <t>91,84; 98,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,85; 91,15</t>
+          <t>83,74; 90,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>83,54; 90,66</t>
+          <t>83,1; 90,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>91,01; 96,22</t>
+          <t>91,36; 96,35</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>84,25; 95,93</t>
+          <t>84,57; 95,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85,61; 96,01</t>
+          <t>85,24; 96,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>75,78; 91,2</t>
+          <t>76,5; 91,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>87,51; 97,33</t>
+          <t>88,32; 97,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>88,55; 98,04</t>
+          <t>88,44; 98,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>76,35; 90,34</t>
+          <t>76,18; 90,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>88,94; 95,87</t>
+          <t>88,46; 95,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>89,01; 95,96</t>
+          <t>89,08; 96,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>79,05; 89,05</t>
+          <t>79,13; 89,38</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>87,55; 97,44</t>
+          <t>87,41; 97,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>84,16; 95,13</t>
+          <t>84,34; 95,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>81,12; 93,21</t>
+          <t>81,6; 93,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>84,94; 96,27</t>
+          <t>85,23; 96,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>83,39; 94,81</t>
+          <t>83,32; 94,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,87; 97,53</t>
+          <t>87,78; 97,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,76; 95,64</t>
+          <t>88,53; 95,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>86,18; 93,89</t>
+          <t>86,23; 94,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>86,84; 94,37</t>
+          <t>86,43; 94,45</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>70,05; 89,2</t>
+          <t>71,06; 89,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>87,58; 98,53</t>
+          <t>87,14; 98,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>82,67; 96,11</t>
+          <t>81,79; 96,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66,19; 86,28</t>
+          <t>67,02; 86,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>87,92; 98,57</t>
+          <t>87,17; 98,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>74,14; 93,08</t>
+          <t>74,9; 92,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,21; 86,07</t>
+          <t>71,62; 86,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>90,61; 98,34</t>
+          <t>90,55; 98,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>81,94; 93,45</t>
+          <t>82,77; 93,63</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>84,59; 96,66</t>
+          <t>85,48; 96,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>82,02; 95,91</t>
+          <t>83,03; 96,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>83,63; 96,46</t>
+          <t>82,04; 96,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>82,64; 94,98</t>
+          <t>82,99; 95,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>83,95; 96,8</t>
+          <t>83,0; 96,51</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>86,75; 97,65</t>
+          <t>86,46; 97,66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>87,06; 95,31</t>
+          <t>86,43; 95,17</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>85,95; 95,39</t>
+          <t>86,02; 95,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>87,5; 95,84</t>
+          <t>87,53; 95,9</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>89,68; 96,82</t>
+          <t>89,42; 96,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>79,9; 90,31</t>
+          <t>79,75; 89,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>87,9; 95,1</t>
+          <t>87,53; 95,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>82,62; 91,91</t>
+          <t>82,46; 91,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>84,78; 93,0</t>
+          <t>84,21; 93,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,59; 92,87</t>
+          <t>84,34; 92,88</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,29; 93,13</t>
+          <t>87,49; 93,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>83,51; 90,1</t>
+          <t>83,93; 90,62</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>87,5; 92,96</t>
+          <t>87,79; 93,24</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>85,88; 93,7</t>
+          <t>85,99; 93,52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>85,32; 92,79</t>
+          <t>84,7; 92,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>85,6; 93,0</t>
+          <t>85,47; 92,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78,43; 87,81</t>
+          <t>78,03; 87,28</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>86,81; 94,19</t>
+          <t>87,8; 94,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>88,98; 95,79</t>
+          <t>89,89; 95,94</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>83,49; 89,49</t>
+          <t>83,32; 89,63</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>87,14; 92,7</t>
+          <t>87,41; 92,67</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>89,27; 93,77</t>
+          <t>88,77; 93,64</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>88,45; 92,0</t>
+          <t>88,33; 91,99</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>86,93; 90,92</t>
+          <t>87,07; 91,03</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>87,75; 91,55</t>
+          <t>87,83; 91,52</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>85,37; 89,35</t>
+          <t>85,31; 89,34</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>89,6; 92,97</t>
+          <t>89,36; 92,96</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>89,47; 92,83</t>
+          <t>89,44; 92,85</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>87,52; 90,17</t>
+          <t>87,53; 90,1</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>88,95; 91,44</t>
+          <t>88,91; 91,53</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>89,15; 91,76</t>
+          <t>89,31; 91,78</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>40252; 48404</t>
+          <t>40524; 48474</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>49668; 55907</t>
+          <t>49243; 55907</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43036; 52121</t>
+          <t>43385; 52313</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47681; 56750</t>
+          <t>48629; 56732</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>55478; 63013</t>
+          <t>55145; 63017</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>52152; 60417</t>
+          <t>51570; 60488</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>92029; 103539</t>
+          <t>92080; 103602</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>107849; 117733</t>
+          <t>107642; 117760</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>98809; 111066</t>
+          <t>98962; 111830</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>82760; 93690</t>
+          <t>83066; 93549</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>82198; 94123</t>
+          <t>82329; 94086</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>91618; 99836</t>
+          <t>90897; 99241</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88988; 100281</t>
+          <t>89675; 100250</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>93463; 104021</t>
+          <t>91983; 103702</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>101590; 108332</t>
+          <t>101283; 108316</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>176346; 191705</t>
+          <t>176115; 191152</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>180344; 195711</t>
+          <t>179387; 195553</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>194974; 206134</t>
+          <t>195730; 206420</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>56949; 64844</t>
+          <t>57166; 64831</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>58369; 65459</t>
+          <t>58113; 65501</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>50644; 60953</t>
+          <t>51122; 61154</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>61545; 68450</t>
+          <t>62115; 68456</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>63093; 69860</t>
+          <t>63019; 69857</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>53369; 63152</t>
+          <t>53255; 63259</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>122675; 132232</t>
+          <t>122001; 132008</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>124111; 133797</t>
+          <t>124211; 133944</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>108090; 121766</t>
+          <t>108199; 122213</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>65541; 72941</t>
+          <t>65439; 72958</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>65440; 73970</t>
+          <t>65584; 74487</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>62427; 71737</t>
+          <t>62803; 71775</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>67197; 76160</t>
+          <t>67426; 76164</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>68574; 77962</t>
+          <t>68519; 78108</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>71339; 79178</t>
+          <t>71267; 79469</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>136664; 147265</t>
+          <t>136315; 147587</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>137879; 150218</t>
+          <t>137967; 150516</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>137326; 149244</t>
+          <t>136690; 149361</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>29319; 37334</t>
+          <t>29739; 37406</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>38449; 43256</t>
+          <t>38253; 43250</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>35912; 41747</t>
+          <t>35528; 42111</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>29681; 38692</t>
+          <t>30053; 38684</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>41106; 46084</t>
+          <t>40755; 46085</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>34364; 43144</t>
+          <t>34715; 43047</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>62606; 74618</t>
+          <t>62090; 75076</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>82141; 89150</t>
+          <t>82088; 89142</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>73570; 83905</t>
+          <t>74322; 84065</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>47419; 54183</t>
+          <t>47918; 54183</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>45921; 53694</t>
+          <t>46482; 53833</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>45390; 52352</t>
+          <t>44524; 52308</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>49363; 56731</t>
+          <t>49570; 56893</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>50577; 58317</t>
+          <t>50001; 58145</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>50091; 56382</t>
+          <t>49921; 56389</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>100804; 110357</t>
+          <t>100074; 110197</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>99898; 110874</t>
+          <t>99977; 110541</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>98010; 107349</t>
+          <t>98042; 107414</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>114053; 123132</t>
+          <t>113724; 122920</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>110084; 124430</t>
+          <t>109875; 123738</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>120757; 130644</t>
+          <t>120237; 130778</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>112082; 124682</t>
+          <t>111861; 124599</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>122716; 134619</t>
+          <t>121892; 135234</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>121864; 133794</t>
+          <t>121507; 133808</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>229418; 244771</t>
+          <t>229957; 245329</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>235932; 254573</t>
+          <t>237130; 256017</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>246274; 261642</t>
+          <t>247075; 262431</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>135606; 147954</t>
+          <t>135781; 147674</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>140528; 152832</t>
+          <t>139512; 152429</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>140527; 152692</t>
+          <t>140315; 152492</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>128671; 144054</t>
+          <t>128022; 143197</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>146954; 159438</t>
+          <t>148620; 160248</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>152030; 163655</t>
+          <t>153570; 163917</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>268813; 288109</t>
+          <t>268259; 288560</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>291047; 309594</t>
+          <t>291940; 309513</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>299079; 314143</t>
+          <t>297409; 313714</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>601092; 625225</t>
+          <t>600298; 625132</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>617612; 645912</t>
+          <t>618615; 646696</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>618103; 644853</t>
+          <t>618652; 644628</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>616993; 645702</t>
+          <t>616543; 645662</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>672442; 697686</t>
+          <t>670650; 697623</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>666379; 691435</t>
+          <t>666188; 691607</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1227233; 1264402</t>
+          <t>1227346; 1263383</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1299481; 1335811</t>
+          <t>1298862; 1337184</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1292026; 1329840</t>
+          <t>1294340; 1330065</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP25-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP25-Provincia-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>88,55%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>92,93%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>88,57%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>86,02%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>93,2%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>84,57%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>88,55%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>92,93%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>88,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>77,09; 92,21</t>
+          <t>81,15; 94,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>85,75; 97,35</t>
+          <t>83,97; 96,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>75,62; 91,18</t>
+          <t>80,97; 93,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>80,76; 94,21</t>
+          <t>77,31; 91,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>85,09; 97,24</t>
+          <t>86,06; 97,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,0; 93,83</t>
+          <t>76,18; 91,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,64; 91,86</t>
+          <t>82,0; 91,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>88,06; 96,34</t>
+          <t>87,6; 96,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>81,23; 91,79</t>
+          <t>81,3; 90,87</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>87,96%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>89,24%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>95,86%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>87,45%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>85,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>92,41%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>87,96%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>89,24%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>95,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>81,79; 92,11</t>
+          <t>82,62; 92,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>78,62; 89,85</t>
+          <t>83,57; 92,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>87,45; 95,47</t>
+          <t>92,31; 98,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>82,45; 92,18</t>
+          <t>80,82; 91,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>82,75; 93,29</t>
+          <t>79,09; 90,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>91,84; 98,22</t>
+          <t>87,08; 95,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,74; 90,89</t>
+          <t>83,81; 90,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>83,1; 90,59</t>
+          <t>82,96; 90,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>91,36; 96,35</t>
+          <t>91,15; 96,21</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>93,74%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>94,25%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>84,15%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>91,68%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>91,88%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>85,29%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>93,74%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>94,25%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>84,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>84,57; 95,91</t>
+          <t>88,27; 97,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85,24; 96,07</t>
+          <t>88,38; 98,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>76,5; 91,51</t>
+          <t>76,11; 90,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88,32; 97,34</t>
+          <t>84,95; 95,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>88,44; 98,04</t>
+          <t>84,81; 96,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>76,18; 90,49</t>
+          <t>76,93; 91,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>88,46; 95,71</t>
+          <t>88,35; 95,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>89,08; 96,06</t>
+          <t>89,02; 96,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>79,13; 89,38</t>
+          <t>79,58; 89,34</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>91,87%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>90,27%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>94,03%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>93,55%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>90,75%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>88,13%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>91,87%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>90,27%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>94,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>87,41; 97,46</t>
+          <t>85,94; 96,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>84,34; 95,79</t>
+          <t>83,43; 94,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>81,6; 93,26</t>
+          <t>87,93; 97,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85,23; 96,28</t>
+          <t>88,09; 97,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>83,32; 94,98</t>
+          <t>84,13; 95,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,78; 97,89</t>
+          <t>80,49; 93,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,53; 95,85</t>
+          <t>88,48; 95,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>86,23; 94,08</t>
+          <t>86,0; 93,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>86,43; 94,45</t>
+          <t>86,06; 94,28</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>78,1%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>95,34%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>86,34%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>81,19%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>95,3%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>91,52%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>78,1%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>95,34%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>86,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>71,06; 89,38</t>
+          <t>67,05; 86,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>87,14; 98,52</t>
+          <t>88,06; 98,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81,79; 96,94</t>
+          <t>75,23; 93,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67,02; 86,27</t>
+          <t>69,98; 89,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>87,17; 98,57</t>
+          <t>87,37; 98,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>74,9; 92,87</t>
+          <t>82,55; 97,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,62; 86,6</t>
+          <t>71,31; 86,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>90,55; 98,33</t>
+          <t>90,87; 98,36</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>82,77; 93,63</t>
+          <t>82,16; 93,46</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>90,5%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>92,08%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>93,97%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>92,92%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>90,94%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>91,06%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>90,5%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>92,08%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>85,48; 96,66</t>
+          <t>83,84; 95,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>83,03; 96,16</t>
+          <t>84,07; 96,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>82,04; 96,38</t>
+          <t>86,79; 97,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>82,99; 95,25</t>
+          <t>84,88; 97,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>83,0; 96,51</t>
+          <t>82,38; 95,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>86,46; 97,66</t>
+          <t>82,3; 95,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>86,43; 95,17</t>
+          <t>86,77; 95,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>86,02; 95,11</t>
+          <t>86,14; 95,06</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>87,53; 95,9</t>
+          <t>87,15; 95,94</t>
         </is>
       </c>
     </row>
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>87,93%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>89,29%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>89,27%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>93,62%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>85,26%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>92,28%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>87,93%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>89,29%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>89,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>89,42; 96,65</t>
+          <t>82,77; 91,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>79,75; 89,81</t>
+          <t>83,91; 93,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>87,53; 95,2</t>
+          <t>84,38; 92,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>82,46; 91,85</t>
+          <t>89,87; 96,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>84,21; 93,42</t>
+          <t>79,88; 89,92</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,34; 92,88</t>
+          <t>88,48; 95,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,49; 93,34</t>
+          <t>87,54; 93,42</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>83,93; 90,62</t>
+          <t>83,85; 90,31</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>87,79; 93,24</t>
+          <t>87,61; 93,24</t>
         </is>
       </c>
     </row>
@@ -1395,32 +1395,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>83,31%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>91,42%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>93,28%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>90,29%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>89,2%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>89,77%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>83,31%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>91,42%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>93,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>85,99; 93,52</t>
+          <t>78,1; 87,59</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>84,7; 92,54</t>
+          <t>87,4; 94,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>85,47; 92,88</t>
+          <t>89,47; 95,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78,03; 87,28</t>
+          <t>85,84; 93,72</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>87,8; 94,67</t>
+          <t>84,41; 92,68</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>89,89; 95,94</t>
+          <t>85,49; 92,79</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>83,32; 89,63</t>
+          <t>83,3; 89,48</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>87,41; 92,67</t>
+          <t>87,47; 92,6</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>88,77; 93,64</t>
+          <t>88,78; 93,64</t>
         </is>
       </c>
     </row>
@@ -1505,32 +1505,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>87,54%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>91,25%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>91,32%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>90,31%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>89,08%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>89,83%</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>87,54%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>91,25%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>91,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>88,33; 91,99</t>
+          <t>85,44; 89,42</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>87,07; 91,03</t>
+          <t>89,46; 92,82</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>87,83; 91,52</t>
+          <t>89,59; 92,99</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>85,31; 89,34</t>
+          <t>88,22; 91,98</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>89,36; 92,96</t>
+          <t>87,15; 90,9</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>89,44; 92,85</t>
+          <t>88,05; 91,54</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>87,53; 90,1</t>
+          <t>87,56; 90,14</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>88,91; 91,53</t>
+          <t>88,85; 91,43</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>89,31; 91,78</t>
+          <t>89,26; 91,8</t>
         </is>
       </c>
     </row>
@@ -1660,14 +1660,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1755,32 +1755,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>79</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1808,32 +1808,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>53324</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>60230</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>57096</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>45219</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>53525</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>48521</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>53324</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>60230</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>57096</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>40524; 48474</t>
+          <t>48865; 56800</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>49243; 55907</t>
+          <t>54423; 62861</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43385; 52313</t>
+          <t>52195; 60365</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>48629; 56732</t>
+          <t>40640; 48304</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>55145; 63017</t>
+          <t>49420; 55883</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>51570; 60488</t>
+          <t>43704; 52429</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>92080; 103602</t>
+          <t>92479; 103564</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>107642; 117760</t>
+          <t>107075; 117514</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>98962; 111830</t>
+          <t>99044; 110705</t>
         </is>
       </c>
     </row>
@@ -1918,32 +1918,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>128</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>144</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1971,32 +1971,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>95665</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>99194</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>105716</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>88817</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>89006</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96056</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>95665</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>99194</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>105716</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>83066; 93549</t>
+          <t>89860; 100176</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>82329; 94086</t>
+          <t>92893; 103258</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>90897; 99241</t>
+          <t>101806; 108341</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>89675; 100250</t>
+          <t>82084; 93108</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>91983; 103702</t>
+          <t>82822; 94549</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>101283; 108316</t>
+          <t>90512; 99357</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>176115; 191152</t>
+          <t>176276; 190950</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>179387; 195553</t>
+          <t>179080; 195155</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>195730; 206420</t>
+          <t>195275; 206121</t>
         </is>
       </c>
     </row>
@@ -2081,32 +2081,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>86</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>74</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -2134,32 +2134,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>65928</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>67158</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>58824</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>61973</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>62641</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>57001</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>65928</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>67158</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>58824</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>57166; 64831</t>
+          <t>62080; 68442</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>58113; 65501</t>
+          <t>62975; 69852</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>51122; 61154</t>
+          <t>53202; 63038</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>62115; 68456</t>
+          <t>57423; 64869</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>63019; 69857</t>
+          <t>57823; 65495</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>53255; 63259</t>
+          <t>51416; 61271</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>122001; 132008</t>
+          <t>121856; 132012</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>124211; 133944</t>
+          <t>124126; 134073</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>108199; 122213</t>
+          <t>108816; 122154</t>
         </is>
       </c>
     </row>
@@ -2249,27 +2249,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>99</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2297,32 +2297,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>72678</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>74230</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>76338</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>70034</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>70571</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>67828</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>72678</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>74230</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>76338</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>65439; 72958</t>
+          <t>67988; 76249</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>65584; 74487</t>
+          <t>68606; 78037</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>62803; 71775</t>
+          <t>71384; 79341</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>67426; 76164</t>
+          <t>65943; 72986</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>68519; 78108</t>
+          <t>65417; 74235</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>71267; 79469</t>
+          <t>61946; 71810</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>136315; 147587</t>
+          <t>136228; 147215</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>137967; 150516</t>
+          <t>137598; 150165</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>136690; 149361</t>
+          <t>136094; 149093</t>
         </is>
       </c>
     </row>
@@ -2407,32 +2407,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>57</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2460,32 +2460,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>35024</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>44573</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>40017</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>33981</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>41837</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>39756</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>35024</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>44573</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>40017</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>29739; 37406</t>
+          <t>30067; 38703</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>38253; 43250</t>
+          <t>41170; 46086</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>35528; 42111</t>
+          <t>34871; 43521</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30053; 38684</t>
+          <t>29290; 37340</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>40755; 46085</t>
+          <t>38357; 43255</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>34715; 43047</t>
+          <t>35858; 42214</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>62090; 75076</t>
+          <t>61825; 74599</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>82088; 89142</t>
+          <t>82374; 89164</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>74322; 84065</t>
+          <t>73772; 83917</t>
         </is>
       </c>
     </row>
@@ -2570,32 +2570,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>72</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>54060</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>55475</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>54255</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>52088</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>50915</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>49423</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>54060</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>55475</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>54255</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>47918; 54183</t>
+          <t>50079; 57001</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>46482; 53833</t>
+          <t>50650; 58098</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>44524; 52308</t>
+          <t>50112; 56394</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>49570; 56893</t>
+          <t>47577; 54670</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>50001; 58145</t>
+          <t>46122; 53706</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>49921; 56389</t>
+          <t>44667; 52007</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>100074; 110197</t>
+          <t>100464; 110088</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>99977; 110541</t>
+          <t>100118; 110487</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>98042; 107414</t>
+          <t>97617; 107460</t>
         </is>
       </c>
     </row>
@@ -2733,32 +2733,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>164</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>190</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2786,32 +2786,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>119276</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>129245</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>128608</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>119070</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>117465</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>126774</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>119276</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>129245</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>128608</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>113724; 122920</t>
+          <t>112278; 124243</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>109875; 123738</t>
+          <t>121466; 134897</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>120237; 130778</t>
+          <t>121572; 133668</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>111861; 124599</t>
+          <t>114298; 123144</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>121892; 135234</t>
+          <t>110050; 123888</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>121507; 133808</t>
+          <t>121551; 130932</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>229957; 245329</t>
+          <t>230086; 245536</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>237130; 256017</t>
+          <t>236912; 255150</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>247075; 262431</t>
+          <t>246578; 262416</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>217</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>219</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>233</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2949,32 +2949,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>136673</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>154748</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>159360</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>142569</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>146922</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>147374</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>136673</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>154748</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>159360</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>135781; 147674</t>
+          <t>128131; 143700</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>139512; 152429</t>
+          <t>147938; 159942</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>140315; 152492</t>
+          <t>152855; 163724</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>128022; 143197</t>
+          <t>135549; 147982</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>148620; 160248</t>
+          <t>139030; 152648</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>153570; 163917</t>
+          <t>140350; 152342</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>268259; 288560</t>
+          <t>268203; 288088</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>291940; 309513</t>
+          <t>292135; 309259</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>297409; 313714</t>
+          <t>297431; 313710</t>
         </is>
       </c>
     </row>
@@ -3059,32 +3059,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>951</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>978</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>971</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>909</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>948</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>951</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>978</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>971</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3112,32 +3112,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>632629</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>684852</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>680214</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>613750</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>632881</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>632732</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>632629</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>684852</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>680214</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>600298; 625132</t>
+          <t>617477; 646203</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>618615; 646696</t>
+          <t>671348; 696627</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>618652; 644628</t>
+          <t>667283; 692635</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>616543; 645662</t>
+          <t>599517; 625109</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>670650; 697623</t>
+          <t>619167; 645775</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>666188; 691607</t>
+          <t>620191; 644772</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1227346; 1263383</t>
+          <t>1227893; 1264024</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1298862; 1337184</t>
+          <t>1298087; 1335683</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1294340; 1330065</t>
+          <t>1293630; 1330342</t>
         </is>
       </c>
     </row>
